--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:27</t>
+    <t xml:space="preserve">2026-09-10 01:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:42</t>
+    <t xml:space="preserve">2026-09-18 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:38</t>
+    <t xml:space="preserve">2026-09-23 15:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_atacama.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:44</t>
+    <t xml:space="preserve">2026-10-05 16:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
